--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E490FA7-FCEE-42F9-B807-BA70A5B49F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041CAC8A-F493-4AE7-BDE6-930144BE68AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="23">
   <si>
     <t>x</t>
   </si>
@@ -186,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -216,12 +216,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -234,8 +228,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -590,31 +587,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="15"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="11"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="15"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -650,13 +647,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11">
-        <v>6</v>
-      </c>
-      <c r="C3" s="11">
+      <c r="B3" s="15">
+        <v>6</v>
+      </c>
+      <c r="C3" s="15">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -691,9 +688,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -729,9 +726,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -767,9 +764,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -805,9 +802,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -837,13 +834,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="15">
         <v>3</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="15">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -877,9 +874,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -915,9 +912,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -953,9 +950,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -991,9 +988,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1029,9 +1026,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1061,13 +1058,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="15">
         <v>11</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="15">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1101,9 +1098,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1139,9 +1136,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1177,9 +1174,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1209,13 +1206,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="15">
         <v>12</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="15">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1250,9 +1247,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1288,9 +1285,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1326,9 +1323,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1364,9 +1361,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1394,6 +1391,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1407,11 +1409,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1438,31 +1435,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="11"/>
+      <c r="I1" s="15"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="11"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="11"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="15"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1498,13 +1495,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="15">
         <v>5</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="15">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -1539,9 +1536,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -1577,9 +1574,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -1615,9 +1612,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1653,9 +1650,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1685,13 +1682,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="15">
         <v>3</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="15">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -1725,9 +1722,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1763,9 +1760,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1801,9 +1798,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1839,9 +1836,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1877,9 +1874,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1909,13 +1906,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="15">
         <v>11</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="15">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1949,9 +1946,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1987,9 +1984,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2025,9 +2022,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2057,13 +2054,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="15">
         <v>11</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="15">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2098,9 +2095,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2136,9 +2133,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2174,9 +2171,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2212,9 +2209,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2250,9 +2247,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2288,9 +2285,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2318,24 +2315,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2389,28 +2386,28 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="11">
-        <v>8</v>
-      </c>
-      <c r="S1" s="11">
+      <c r="R1" s="15">
+        <v>8</v>
+      </c>
+      <c r="S1" s="15">
         <v>7</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11" t="s">
+      <c r="V1" s="15"/>
+      <c r="W1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11" t="s">
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11">
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15">
         <v>8.9</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -2436,8 +2433,8 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
       <c r="U2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2456,7 +2453,7 @@
       <c r="Z2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="11"/>
+      <c r="AA2" s="15"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -2477,8 +2474,8 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
       <c r="T3" s="1">
         <v>1</v>
       </c>
@@ -2488,19 +2485,19 @@
       <c r="V3" s="1">
         <v>8</v>
       </c>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="16">
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14">
         <f>$R$1 + AB3</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="16">
+      <c r="AF3" s="14">
         <f>$S$1+AC3</f>
         <v>7</v>
       </c>
@@ -2524,8 +2521,8 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
       <c r="T4" s="1">
         <v>2</v>
       </c>
@@ -2535,19 +2532,19 @@
       <c r="V4" s="1">
         <v>8</v>
       </c>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="16">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="16"/>
-      <c r="AE4" s="16">
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="14">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14">
         <f t="shared" ref="AE4:AE11" si="0">$R$1 + AB4</f>
         <v>8</v>
       </c>
-      <c r="AF4" s="16">
+      <c r="AF4" s="14">
         <f t="shared" ref="AF4:AF11" si="1">$S$1+AC4</f>
         <v>8</v>
       </c>
@@ -2571,8 +2568,8 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
       <c r="T5" s="1">
         <v>3</v>
       </c>
@@ -2594,7 +2591,7 @@
       <c r="Z5" s="1">
         <v>6</v>
       </c>
-      <c r="AA5" s="11"/>
+      <c r="AA5" s="15"/>
       <c r="AB5" s="1">
         <v>0</v>
       </c>
@@ -2629,8 +2626,8 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
       <c r="T6" s="1">
         <v>4</v>
       </c>
@@ -2652,19 +2649,19 @@
       <c r="Z6" s="1">
         <v>8</v>
       </c>
-      <c r="AA6" s="11"/>
-      <c r="AB6" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF6" s="17">
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="14">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF6" s="14">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -2688,8 +2685,8 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
       <c r="T7" s="1">
         <v>5</v>
       </c>
@@ -2711,7 +2708,7 @@
       <c r="Z7" s="1">
         <v>6</v>
       </c>
-      <c r="AA7" s="11"/>
+      <c r="AA7" s="15"/>
       <c r="AB7" s="1">
         <v>1</v>
       </c>
@@ -2748,8 +2745,8 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
       <c r="T8" s="1">
         <v>6</v>
       </c>
@@ -2771,7 +2768,7 @@
       <c r="Z8" s="1">
         <v>6</v>
       </c>
-      <c r="AA8" s="11"/>
+      <c r="AA8" s="15"/>
       <c r="AB8" s="1">
         <v>1</v>
       </c>
@@ -2797,19 +2794,23 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="I9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="K9" s="10"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
       <c r="T9" s="1">
         <v>7</v>
       </c>
@@ -2831,25 +2832,25 @@
       <c r="Z9" s="1">
         <v>8</v>
       </c>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="17">
-        <v>-1</v>
-      </c>
-      <c r="AC9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF9" s="17">
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="14">
+        <v>-1</v>
+      </c>
+      <c r="AC9" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AF9" s="14">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="13">
         <v>7</v>
       </c>
       <c r="B10" s="7"/>
@@ -2861,7 +2862,7 @@
       <c r="H10" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="11" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="7" t="s">
@@ -2873,8 +2874,8 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
       <c r="T10" s="1">
         <v>8</v>
       </c>
@@ -2896,7 +2897,7 @@
       <c r="Z10" s="1">
         <v>8</v>
       </c>
-      <c r="AA10" s="11"/>
+      <c r="AA10" s="15"/>
       <c r="AB10" s="1">
         <v>-1</v>
       </c>
@@ -2933,12 +2934,12 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
       <c r="T11" s="1">
         <v>9</v>
       </c>
-      <c r="AA11" s="11"/>
+      <c r="AA11" s="15"/>
       <c r="AB11" s="1">
         <v>-1</v>
       </c>
@@ -2973,12 +2974,12 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
       <c r="T12" s="1">
         <v>10</v>
       </c>
-      <c r="AA12" s="11"/>
+      <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -2999,12 +3000,12 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
       <c r="T13" s="1">
         <v>11</v>
       </c>
-      <c r="AA13" s="11"/>
+      <c r="AA13" s="15"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -3025,12 +3026,12 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
       <c r="T14" s="1">
         <v>12</v>
       </c>
-      <c r="AA14" s="11"/>
+      <c r="AA14" s="15"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -3051,12 +3052,12 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
       <c r="T15" s="1">
         <v>13</v>
       </c>
-      <c r="AA15" s="11"/>
+      <c r="AA15" s="15"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -3103,7 +3104,7 @@
       <c r="H17" s="9">
         <v>7</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="12">
         <v>8</v>
       </c>
       <c r="J17" s="9">

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041CAC8A-F493-4AE7-BDE6-930144BE68AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770308BF-1AD7-46B4-8627-7F9FC8F84245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="23">
   <si>
     <t>x</t>
   </si>
@@ -117,7 +117,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,8 +138,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,6 +161,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -186,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +251,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2486,20 +2516,20 @@
         <v>8</v>
       </c>
       <c r="AA3" s="15"/>
-      <c r="AB3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14">
+      <c r="AB3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="18">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="18"/>
+      <c r="AE3" s="18">
         <f>$R$1 + AB3</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="14">
+      <c r="AF3" s="18">
         <f>$S$1+AC3</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -2533,18 +2563,18 @@
         <v>8</v>
       </c>
       <c r="AA4" s="15"/>
-      <c r="AB4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="14">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14">
+      <c r="AB4" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="18">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="18"/>
+      <c r="AE4" s="18">
         <f t="shared" ref="AE4:AE11" si="0">$R$1 + AB4</f>
-        <v>8</v>
-      </c>
-      <c r="AF4" s="14">
+        <v>9</v>
+      </c>
+      <c r="AF4" s="18">
         <f t="shared" ref="AF4:AF11" si="1">$S$1+AC4</f>
         <v>8</v>
       </c>
@@ -2592,19 +2622,20 @@
         <v>6</v>
       </c>
       <c r="AA5" s="15"/>
-      <c r="AB5" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AE5" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AF5" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
+      <c r="AB5" s="14">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF5" s="14">
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -2650,20 +2681,20 @@
         <v>8</v>
       </c>
       <c r="AA6" s="15"/>
-      <c r="AB6" s="14">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="14"/>
-      <c r="AE6" s="14">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF6" s="14">
-        <f t="shared" si="1"/>
-        <v>7</v>
+      <c r="AB6" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="18">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="18"/>
+      <c r="AE6" s="18">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF6" s="18">
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -2710,18 +2741,18 @@
       </c>
       <c r="AA7" s="15"/>
       <c r="AB7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AE7" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF7" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -2735,7 +2766,7 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="20" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="7"/>
@@ -2770,14 +2801,14 @@
       </c>
       <c r="AA8" s="15"/>
       <c r="AB8" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AC8" s="1">
         <v>-1</v>
       </c>
       <c r="AE8" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF8" s="1">
         <f t="shared" si="1"/>
@@ -2794,7 +2825,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="20" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -2858,17 +2889,17 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="G10" s="20"/>
       <c r="H10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7"/>
+      <c r="J10" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="19"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -2923,12 +2954,16 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="I11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="19"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2940,20 +2975,6 @@
         <v>9</v>
       </c>
       <c r="AA11" s="15"/>
-      <c r="AB11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AE11" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF11" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -2966,9 +2987,9 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770308BF-1AD7-46B4-8627-7F9FC8F84245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4420454-6C95-4F16-88F9-FA0F337B132E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
-    <sheet name="Tabelle2 (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="sectors" sheetId="1" r:id="rId3"/>
+    <sheet name="sectors DO Not Delete" sheetId="4" r:id="rId2"/>
+    <sheet name="Tabelle2 (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="sectors" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -204,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -246,23 +247,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -617,31 +639,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="16" t="s">
+      <c r="G1" s="19"/>
+      <c r="H1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="15"/>
+      <c r="I1" s="19"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="15"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="19"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -677,13 +699,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="19">
         <v>6</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="19">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -718,9 +740,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -756,9 +778,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -794,9 +816,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -832,9 +854,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -864,13 +886,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="19">
         <v>3</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -904,9 +926,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -942,9 +964,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -980,9 +1002,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1018,9 +1040,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1056,9 +1078,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1088,13 +1110,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="19">
         <v>11</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1128,9 +1150,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1166,9 +1188,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1204,9 +1226,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1236,13 +1258,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="19">
         <v>12</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="19">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1277,9 +1299,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1315,9 +1337,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1353,9 +1375,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1391,9 +1413,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1421,11 +1443,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1439,12 +1456,503 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CE657A-E8E6-49BC-968A-8EBB605481D3}">
+  <dimension ref="A1:AF17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" style="22" customWidth="1"/>
+    <col min="3" max="5" width="2.5703125" style="22" customWidth="1"/>
+    <col min="6" max="6" width="2.85546875" style="22" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" style="22" customWidth="1"/>
+    <col min="9" max="10" width="2.85546875" style="22" customWidth="1"/>
+    <col min="11" max="16" width="3" style="22" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="22"/>
+    <col min="18" max="19" width="2" style="22" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.140625" style="22" customWidth="1"/>
+    <col min="22" max="22" width="5.140625" style="22" customWidth="1"/>
+    <col min="23" max="23" width="4.28515625" style="22" customWidth="1"/>
+    <col min="24" max="24" width="5.28515625" style="22" customWidth="1"/>
+    <col min="25" max="25" width="6.42578125" style="22" customWidth="1"/>
+    <col min="26" max="26" width="3.85546875" style="22" customWidth="1"/>
+    <col min="27" max="27" width="4.28515625" style="22" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="2.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="1.85546875" style="22" customWidth="1"/>
+    <col min="31" max="32" width="2.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="11.42578125" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="20">
+        <v>15</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="AA2" s="23"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
+        <v>14</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
+        <v>13</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
+        <v>12</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>11</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>10</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="AA7" s="23"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>9</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="AA8" s="23"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>7</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="AA10" s="23"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
+        <v>6</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="AA11" s="23"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>5</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="AA12" s="23"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <v>4</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="AA13" s="23"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
+        <v>3</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="AA14" s="23"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
+        <v>2</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="AA15" s="23"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
+        <v>1</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+    </row>
+    <row r="17" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <v>0</v>
+      </c>
+      <c r="B17" s="27">
+        <v>1</v>
+      </c>
+      <c r="C17" s="27">
+        <v>2</v>
+      </c>
+      <c r="D17" s="27">
+        <v>3</v>
+      </c>
+      <c r="E17" s="27">
+        <v>4</v>
+      </c>
+      <c r="F17" s="27">
+        <v>5</v>
+      </c>
+      <c r="G17" s="27">
+        <v>6</v>
+      </c>
+      <c r="H17" s="27">
+        <v>7</v>
+      </c>
+      <c r="I17" s="27">
+        <v>8</v>
+      </c>
+      <c r="J17" s="27">
+        <v>9</v>
+      </c>
+      <c r="K17" s="27">
+        <v>10</v>
+      </c>
+      <c r="L17" s="27">
+        <v>11</v>
+      </c>
+      <c r="M17" s="27">
+        <v>12</v>
+      </c>
+      <c r="N17" s="27">
+        <v>13</v>
+      </c>
+      <c r="O17" s="27">
+        <v>14</v>
+      </c>
+      <c r="P17" s="27">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="R1:R15"/>
+    <mergeCell ref="S1:S15"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AA15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70F40C4-1548-4272-985C-F206499A529C}">
   <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1465,31 +1973,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="16" t="s">
+      <c r="G1" s="19"/>
+      <c r="H1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="15"/>
+      <c r="I1" s="19"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="15"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="19"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1525,13 +2033,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="19">
         <v>5</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="19">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -1566,9 +2074,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -1604,9 +2112,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -1642,9 +2150,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1680,9 +2188,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1712,13 +2220,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="19">
         <v>3</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="19">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -1752,9 +2260,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1790,9 +2298,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1828,9 +2336,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1866,9 +2374,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1904,9 +2412,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1936,13 +2444,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="19">
         <v>11</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="19">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1976,9 +2484,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2014,9 +2522,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2052,9 +2560,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2084,13 +2592,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="19">
         <v>11</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="19">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2125,9 +2633,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2163,9 +2671,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2201,9 +2709,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2239,9 +2747,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2277,9 +2785,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2315,9 +2823,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2345,30 +2853,30 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2347942F-AF0E-41C5-857F-C5F4BF6CCB09}">
   <dimension ref="A1:AF17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2416,28 +2924,28 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="15">
-        <v>8</v>
-      </c>
-      <c r="S1" s="15">
+      <c r="R1" s="19">
+        <v>8</v>
+      </c>
+      <c r="S1" s="19">
         <v>7</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="U1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15" t="s">
+      <c r="V1" s="19"/>
+      <c r="W1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15" t="s">
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15">
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19">
         <v>8.9</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -2463,8 +2971,8 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
       <c r="U2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2483,7 +2991,7 @@
       <c r="Z2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="15"/>
+      <c r="AA2" s="19"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -2504,8 +3012,8 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
       <c r="T3" s="1">
         <v>1</v>
       </c>
@@ -2515,19 +3023,19 @@
       <c r="V3" s="1">
         <v>8</v>
       </c>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="18">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="18"/>
-      <c r="AE3" s="18">
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="16">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16">
         <f>$R$1 + AB3</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="18">
+      <c r="AF3" s="16">
         <f>$S$1+AC3</f>
         <v>8</v>
       </c>
@@ -2551,8 +3059,8 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
       <c r="T4" s="1">
         <v>2</v>
       </c>
@@ -2562,20 +3070,20 @@
       <c r="V4" s="1">
         <v>8</v>
       </c>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="18">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="18">
-        <f t="shared" ref="AE4:AE11" si="0">$R$1 + AB4</f>
-        <v>9</v>
-      </c>
-      <c r="AF4" s="18">
-        <f t="shared" ref="AF4:AF11" si="1">$S$1+AC4</f>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="16">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="16">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16">
+        <f t="shared" ref="AE4:AE10" si="0">$R$1 + AB4</f>
+        <v>9</v>
+      </c>
+      <c r="AF4" s="16">
+        <f t="shared" ref="AF4:AF10" si="1">$S$1+AC4</f>
         <v>8</v>
       </c>
     </row>
@@ -2598,8 +3106,8 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
       <c r="T5" s="1">
         <v>3</v>
       </c>
@@ -2621,7 +3129,7 @@
       <c r="Z5" s="1">
         <v>6</v>
       </c>
-      <c r="AA5" s="15"/>
+      <c r="AA5" s="19"/>
       <c r="AB5" s="14">
         <v>1</v>
       </c>
@@ -2657,8 +3165,8 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
       <c r="T6" s="1">
         <v>4</v>
       </c>
@@ -2680,19 +3188,19 @@
       <c r="Z6" s="1">
         <v>8</v>
       </c>
-      <c r="AA6" s="15"/>
-      <c r="AB6" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="18">
-        <v>-1</v>
-      </c>
-      <c r="AD6" s="18"/>
-      <c r="AE6" s="18">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF6" s="18">
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="16">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="16">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF6" s="16">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -2716,8 +3224,8 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
       <c r="T7" s="1">
         <v>5</v>
       </c>
@@ -2739,7 +3247,7 @@
       <c r="Z7" s="1">
         <v>6</v>
       </c>
-      <c r="AA7" s="15"/>
+      <c r="AA7" s="19"/>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
@@ -2766,7 +3274,7 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="7"/>
@@ -2776,8 +3284,8 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
       <c r="T8" s="1">
         <v>6</v>
       </c>
@@ -2799,7 +3307,7 @@
       <c r="Z8" s="1">
         <v>6</v>
       </c>
-      <c r="AA8" s="15"/>
+      <c r="AA8" s="19"/>
       <c r="AB8" s="1">
         <v>-1</v>
       </c>
@@ -2825,7 +3333,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -2840,8 +3348,8 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
       <c r="T9" s="1">
         <v>7</v>
       </c>
@@ -2863,7 +3371,7 @@
       <c r="Z9" s="1">
         <v>8</v>
       </c>
-      <c r="AA9" s="15"/>
+      <c r="AA9" s="19"/>
       <c r="AB9" s="14">
         <v>-1</v>
       </c>
@@ -2889,24 +3397,24 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="20"/>
+      <c r="G10" s="17"/>
       <c r="H10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" s="19"/>
+      <c r="J10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
       <c r="T10" s="1">
         <v>8</v>
       </c>
@@ -2928,7 +3436,7 @@
       <c r="Z10" s="1">
         <v>8</v>
       </c>
-      <c r="AA10" s="15"/>
+      <c r="AA10" s="19"/>
       <c r="AB10" s="1">
         <v>-1</v>
       </c>
@@ -2954,27 +3462,27 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="19"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
       <c r="T11" s="1">
         <v>9</v>
       </c>
-      <c r="AA11" s="15"/>
+      <c r="AA11" s="19"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -2987,20 +3495,20 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
       <c r="T12" s="1">
         <v>10</v>
       </c>
-      <c r="AA12" s="15"/>
+      <c r="AA12" s="19"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -3021,12 +3529,12 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
       <c r="T13" s="1">
         <v>11</v>
       </c>
-      <c r="AA13" s="15"/>
+      <c r="AA13" s="19"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -3047,12 +3555,12 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
       <c r="T14" s="1">
         <v>12</v>
       </c>
-      <c r="AA14" s="15"/>
+      <c r="AA14" s="19"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -3073,12 +3581,12 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
       <c r="T15" s="1">
         <v>13</v>
       </c>
-      <c r="AA15" s="15"/>
+      <c r="AA15" s="19"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4420454-6C95-4F16-88F9-FA0F337B132E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AE0501-B023-4EC4-AE46-5CE3496679E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="43530" yWindow="0" windowWidth="13140" windowHeight="16200" activeTab="3" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="23">
   <si>
     <t>x</t>
   </si>
@@ -146,7 +146,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,13 +167,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -205,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -238,53 +232,29 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -639,31 +609,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="18" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="14"/>
+      <c r="H1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="19"/>
+      <c r="I1" s="14"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="19"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="19"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="14"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -699,13 +669,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="14">
         <v>6</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="14">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -740,9 +710,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -778,9 +748,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -816,9 +786,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -854,9 +824,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -886,13 +856,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="14">
         <v>3</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="14">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -926,9 +896,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -964,9 +934,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1002,9 +972,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1040,9 +1010,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1078,9 +1048,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1110,13 +1080,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="14">
         <v>11</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="14">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1150,9 +1120,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1188,9 +1158,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1226,9 +1196,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1258,13 +1228,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="14">
         <v>12</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="14">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1299,9 +1269,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1337,9 +1307,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1375,9 +1345,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1413,9 +1383,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1443,6 +1413,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1456,11 +1431,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1471,481 +1441,481 @@
   <dimension ref="A1:AF17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.42578125" style="22" customWidth="1"/>
-    <col min="3" max="5" width="2.5703125" style="22" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="22" customWidth="1"/>
-    <col min="7" max="7" width="2.5703125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" style="22" customWidth="1"/>
-    <col min="9" max="10" width="2.85546875" style="22" customWidth="1"/>
-    <col min="11" max="16" width="3" style="22" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="22"/>
-    <col min="18" max="19" width="2" style="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" style="22" customWidth="1"/>
-    <col min="22" max="22" width="5.140625" style="22" customWidth="1"/>
-    <col min="23" max="23" width="4.28515625" style="22" customWidth="1"/>
-    <col min="24" max="24" width="5.28515625" style="22" customWidth="1"/>
-    <col min="25" max="25" width="6.42578125" style="22" customWidth="1"/>
-    <col min="26" max="26" width="3.85546875" style="22" customWidth="1"/>
-    <col min="27" max="27" width="4.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="2.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="1.85546875" style="22" customWidth="1"/>
-    <col min="31" max="32" width="2.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="11.42578125" style="22"/>
+    <col min="1" max="1" width="3" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" style="1" customWidth="1"/>
+    <col min="3" max="5" width="2.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="2.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="1"/>
+    <col min="18" max="19" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="5.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="5.28515625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="6.42578125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="3.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="1.85546875" style="1" customWidth="1"/>
+    <col min="31" max="32" width="2.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="20">
+      <c r="A1" s="8">
         <v>15</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="AA2" s="23"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="AA2" s="14"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+      <c r="A3" s="8">
         <v>14</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="AA3" s="23"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="13"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="A4" s="8">
         <v>13</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="AA4" s="23"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="13"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="A5" s="8">
         <v>12</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="12"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="12"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="8">
         <v>11</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="A7" s="8">
         <v>10</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="AA7" s="23"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="AA7" s="14"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
-        <v>9</v>
-      </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="AA8" s="23"/>
+      <c r="A8" s="8">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="AA8" s="14"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
-        <v>8</v>
-      </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-      <c r="AF9" s="25"/>
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="12"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="12"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="12"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
-        <v>7</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="AA10" s="23"/>
+      <c r="A10" s="8">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="AA10" s="14"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
+      <c r="A11" s="8">
         <v>6</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="AA11" s="23"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="AA11" s="14"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+      <c r="A12" s="8">
         <v>5</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="AA12" s="23"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="AA12" s="14"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
+      <c r="A13" s="8">
         <v>4</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="AA13" s="23"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="AA13" s="14"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="8">
         <v>3</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="AA14" s="23"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="AA14" s="14"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+      <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="AA15" s="23"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="AA15" s="14"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
-        <v>1</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-    </row>
-    <row r="17" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="27">
-        <v>0</v>
-      </c>
-      <c r="B17" s="27">
-        <v>1</v>
-      </c>
-      <c r="C17" s="27">
+      <c r="A16" s="8">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+    </row>
+    <row r="17" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>0</v>
+      </c>
+      <c r="B17" s="9">
+        <v>1</v>
+      </c>
+      <c r="C17" s="9">
         <v>2</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="9">
         <v>3</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="9">
         <v>4</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="9">
         <v>5</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="9">
         <v>6</v>
       </c>
-      <c r="H17" s="27">
-        <v>7</v>
-      </c>
-      <c r="I17" s="27">
-        <v>8</v>
-      </c>
-      <c r="J17" s="27">
-        <v>9</v>
-      </c>
-      <c r="K17" s="27">
+      <c r="H17" s="9">
+        <v>7</v>
+      </c>
+      <c r="I17" s="9">
+        <v>8</v>
+      </c>
+      <c r="J17" s="9">
+        <v>9</v>
+      </c>
+      <c r="K17" s="9">
         <v>10</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="9">
         <v>11</v>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="9">
         <v>12</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="9">
         <v>13</v>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="9">
         <v>14</v>
       </c>
-      <c r="P17" s="27">
+      <c r="P17" s="9">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="AA1:AA15"/>
     <mergeCell ref="R1:R15"/>
     <mergeCell ref="S1:S15"/>
     <mergeCell ref="U1:V1"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AA15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1973,31 +1943,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="18" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="14"/>
+      <c r="H1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="19"/>
+      <c r="I1" s="14"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="19"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="19"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="14"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2033,13 +2003,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="14">
         <v>5</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="14">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2074,9 +2044,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2112,9 +2082,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2150,9 +2120,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2188,9 +2158,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2220,13 +2190,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="14">
         <v>3</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="14">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2260,9 +2230,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2298,9 +2268,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2336,9 +2306,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2374,9 +2344,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2412,9 +2382,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2444,13 +2414,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="14">
         <v>11</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="14">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2484,9 +2454,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2522,9 +2492,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2560,9 +2530,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2592,13 +2562,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="14">
         <v>11</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="14">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2633,9 +2603,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2671,9 +2641,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2709,9 +2679,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2747,9 +2717,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2785,9 +2755,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2823,9 +2793,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2853,24 +2823,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2924,28 +2894,28 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="19">
-        <v>8</v>
-      </c>
-      <c r="S1" s="19">
+      <c r="R1" s="14">
+        <v>8</v>
+      </c>
+      <c r="S1" s="14">
         <v>7</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19" t="s">
+      <c r="V1" s="14"/>
+      <c r="W1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19" t="s">
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19">
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14">
         <v>8.9</v>
       </c>
       <c r="AB1" s="1" t="s">
@@ -2956,6 +2926,9 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>14</v>
+      </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -2971,8 +2944,8 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
       <c r="U2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2991,11 +2964,11 @@
       <c r="Z2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="19"/>
+      <c r="AA2" s="14"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3012,8 +2985,8 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
       <c r="T3" s="1">
         <v>1</v>
       </c>
@@ -3023,26 +2996,26 @@
       <c r="V3" s="1">
         <v>8</v>
       </c>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="16">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="16">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="16">
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13">
         <f>$R$1 + AB3</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="16">
+      <c r="AF3" s="13">
         <f>$S$1+AC3</f>
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -3059,8 +3032,8 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
       <c r="T4" s="1">
         <v>2</v>
       </c>
@@ -3070,26 +3043,26 @@
       <c r="V4" s="1">
         <v>8</v>
       </c>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="16">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="16">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="16"/>
-      <c r="AE4" s="16">
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="13">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13">
         <f t="shared" ref="AE4:AE10" si="0">$R$1 + AB4</f>
         <v>9</v>
       </c>
-      <c r="AF4" s="16">
+      <c r="AF4" s="13">
         <f t="shared" ref="AF4:AF10" si="1">$S$1+AC4</f>
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -3106,8 +3079,8 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
       <c r="T5" s="1">
         <v>3</v>
       </c>
@@ -3129,26 +3102,26 @@
       <c r="Z5" s="1">
         <v>6</v>
       </c>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="14">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF5" s="14">
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF5" s="12">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -3165,8 +3138,8 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
       <c r="T6" s="1">
         <v>4</v>
       </c>
@@ -3188,26 +3161,26 @@
       <c r="Z6" s="1">
         <v>8</v>
       </c>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="16">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="16">
-        <v>-1</v>
-      </c>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="16">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF6" s="16">
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="13">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="AF6" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -3224,8 +3197,8 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
       <c r="T7" s="1">
         <v>5</v>
       </c>
@@ -3247,7 +3220,7 @@
       <c r="Z7" s="1">
         <v>6</v>
       </c>
-      <c r="AA7" s="19"/>
+      <c r="AA7" s="14"/>
       <c r="AB7" s="1">
         <v>0</v>
       </c>
@@ -3265,7 +3238,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -3284,8 +3257,8 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
       <c r="T8" s="1">
         <v>6</v>
       </c>
@@ -3307,7 +3280,7 @@
       <c r="Z8" s="1">
         <v>6</v>
       </c>
-      <c r="AA8" s="19"/>
+      <c r="AA8" s="14"/>
       <c r="AB8" s="1">
         <v>-1</v>
       </c>
@@ -3325,31 +3298,47 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="E9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="F9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
+      <c r="G9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
       <c r="T9" s="1">
         <v>7</v>
       </c>
@@ -3371,26 +3360,26 @@
       <c r="Z9" s="1">
         <v>8</v>
       </c>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AC9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF9" s="14">
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="12">
+        <v>-1</v>
+      </c>
+      <c r="AC9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="12"/>
+      <c r="AE9" s="12">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="AF9" s="12">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
-        <v>7</v>
+      <c r="A10" s="8">
+        <v>6</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -3413,8 +3402,8 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
       <c r="T10" s="1">
         <v>8</v>
       </c>
@@ -3436,7 +3425,7 @@
       <c r="Z10" s="1">
         <v>8</v>
       </c>
-      <c r="AA10" s="19"/>
+      <c r="AA10" s="14"/>
       <c r="AB10" s="1">
         <v>-1</v>
       </c>
@@ -3454,39 +3443,43 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="17" t="s">
+      <c r="G11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="7"/>
+      <c r="K11" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
       <c r="T11" s="1">
         <v>9</v>
       </c>
-      <c r="AA11" s="19"/>
+      <c r="AA11" s="14"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3503,16 +3496,16 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
       <c r="T12" s="1">
         <v>10</v>
       </c>
-      <c r="AA12" s="19"/>
+      <c r="AA12" s="14"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -3529,16 +3522,16 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
       <c r="T13" s="1">
         <v>11</v>
       </c>
-      <c r="AA13" s="19"/>
+      <c r="AA13" s="14"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -3555,16 +3548,16 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
       <c r="T14" s="1">
         <v>12</v>
       </c>
-      <c r="AA14" s="19"/>
+      <c r="AA14" s="14"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -3581,16 +3574,16 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
       <c r="T15" s="1">
         <v>13</v>
       </c>
-      <c r="AA15" s="19"/>
+      <c r="AA15" s="14"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -3608,54 +3601,51 @@
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
     </row>
-    <row r="17" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>0</v>
-      </c>
+    <row r="17" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9">
         <v>2</v>
       </c>
-      <c r="D17" s="9">
+      <c r="E17" s="9">
         <v>3</v>
       </c>
-      <c r="E17" s="9">
+      <c r="F17" s="9">
         <v>4</v>
       </c>
-      <c r="F17" s="9">
+      <c r="G17" s="9">
         <v>5</v>
       </c>
-      <c r="G17" s="9">
+      <c r="H17" s="9">
         <v>6</v>
       </c>
-      <c r="H17" s="9">
-        <v>7</v>
-      </c>
-      <c r="I17" s="12">
-        <v>8</v>
+      <c r="I17" s="9">
+        <v>7</v>
       </c>
       <c r="J17" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K17" s="9">
+        <v>9</v>
+      </c>
+      <c r="L17" s="9">
         <v>10</v>
       </c>
-      <c r="L17" s="9">
+      <c r="M17" s="9">
         <v>11</v>
       </c>
-      <c r="M17" s="9">
+      <c r="N17" s="9">
         <v>12</v>
       </c>
-      <c r="N17" s="9">
+      <c r="O17" s="9">
         <v>13</v>
       </c>
-      <c r="O17" s="9">
+      <c r="P17" s="9">
         <v>14</v>
-      </c>
-      <c r="P17" s="9">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AE0501-B023-4EC4-AE46-5CE3496679E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A510AC44-9A2C-498D-AF64-801DD9544E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43530" yWindow="0" windowWidth="13140" windowHeight="16200" activeTab="3" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
     <sheet name="sectors DO Not Delete" sheetId="4" r:id="rId2"/>
     <sheet name="Tabelle2 (2)" sheetId="3" r:id="rId3"/>
     <sheet name="sectors" sheetId="1" r:id="rId4"/>
+    <sheet name="Tabelle1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="26">
   <si>
     <t>x</t>
   </si>
@@ -102,16 +103,25 @@
     <t>↑</t>
   </si>
   <si>
-    <t>z</t>
+    <t>↗</t>
   </si>
   <si>
-    <t>R</t>
+    <t>↖</t>
   </si>
   <si>
-    <t>s</t>
+    <t>←</t>
   </si>
   <si>
-    <t>sector</t>
+    <t>→</t>
+  </si>
+  <si>
+    <t>↘</t>
+  </si>
+  <si>
+    <t>↙</t>
+  </si>
+  <si>
+    <t>↓</t>
   </si>
 </sst>
 </file>
@@ -146,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,13 +171,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -199,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -229,13 +233,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -244,16 +248,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1413,11 +1430,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1431,6 +1443,11 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1536,11 +1553,11 @@
       <c r="R3" s="14"/>
       <c r="S3" s="14"/>
       <c r="AA3" s="14"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="13"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
@@ -1564,11 +1581,11 @@
       <c r="R4" s="14"/>
       <c r="S4" s="14"/>
       <c r="AA4" s="14"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="13"/>
+      <c r="AB4" s="12"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
@@ -1592,11 +1609,11 @@
       <c r="R5" s="14"/>
       <c r="S5" s="14"/>
       <c r="AA5" s="14"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="12"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -1620,11 +1637,11 @@
       <c r="R6" s="14"/>
       <c r="S6" s="14"/>
       <c r="AA6" s="14"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
@@ -1694,11 +1711,11 @@
       <c r="R9" s="14"/>
       <c r="S9" s="14"/>
       <c r="AA9" s="14"/>
-      <c r="AB9" s="12"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="12"/>
-      <c r="AE9" s="12"/>
-      <c r="AF9" s="12"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
@@ -2823,24 +2840,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2848,39 +2865,37 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2347942F-AF0E-41C5-857F-C5F4BF6CCB09}">
-  <dimension ref="A1:AF17"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.42578125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="2.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="2.85546875" style="1" customWidth="1"/>
-    <col min="11" max="16" width="3" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="1"/>
-    <col min="18" max="19" width="2" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="5.140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="4.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="5.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="6.42578125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="3.85546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="1.85546875" style="1" customWidth="1"/>
-    <col min="31" max="32" width="2.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="11.42578125" style="1"/>
+    <col min="2" max="3" width="3" style="8" customWidth="1"/>
+    <col min="4" max="4" width="2.42578125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="2.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="2.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="2.85546875" style="1" customWidth="1"/>
+    <col min="13" max="18" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" style="1"/>
+    <col min="20" max="21" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="5.140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="4.28515625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="5.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="6.42578125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="3.85546875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="1.85546875" style="1" customWidth="1"/>
+    <col min="33" max="34" width="2.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
-        <v>15</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+    <row r="1" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -2894,43 +2909,21 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="14">
-        <v>8</v>
-      </c>
-      <c r="S1" s="14">
-        <v>7</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="W1" s="14"/>
       <c r="X1" s="14"/>
-      <c r="Y1" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="Y1" s="14"/>
       <c r="Z1" s="14"/>
-      <c r="AA1" s="14">
-        <v>8.9</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>14</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+    </row>
+    <row r="2" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -2944,37 +2937,18 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="U2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="14"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>13</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="AC2" s="14"/>
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="10"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -2985,41 +2959,21 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="1">
-        <v>1</v>
-      </c>
-      <c r="U3" s="1">
-        <v>7</v>
-      </c>
-      <c r="V3" s="1">
-        <v>8</v>
-      </c>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="13">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13">
-        <f>$R$1 + AB3</f>
-        <v>8</v>
-      </c>
-      <c r="AF3" s="13">
-        <f>$S$1+AC3</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="12"/>
+    </row>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -3032,45 +2986,25 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="1">
-        <v>2</v>
-      </c>
-      <c r="U4" s="1">
-        <v>9</v>
-      </c>
-      <c r="V4" s="1">
-        <v>8</v>
-      </c>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="13">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="13">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="13">
-        <f t="shared" ref="AE4:AE10" si="0">$R$1 + AB4</f>
-        <v>9</v>
-      </c>
-      <c r="AF4" s="13">
-        <f t="shared" ref="AF4:AF10" si="1">$S$1+AC4</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>11</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="12"/>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3079,55 +3013,23 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="1">
-        <v>3</v>
-      </c>
-      <c r="U5" s="1">
-        <v>8</v>
-      </c>
-      <c r="V5" s="1">
-        <v>6</v>
-      </c>
-      <c r="W5" s="1">
-        <v>7</v>
-      </c>
-      <c r="X5" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>7</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF5" s="12">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>10</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+    </row>
+    <row r="6" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -3135,529 +3037,725 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="N6" s="21"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="1">
-        <v>4</v>
-      </c>
-      <c r="U6" s="1">
-        <v>8</v>
-      </c>
-      <c r="V6" s="1">
-        <v>6</v>
-      </c>
-      <c r="W6" s="1">
-        <v>9</v>
-      </c>
-      <c r="X6" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>8</v>
-      </c>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="13">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="13">
-        <v>-1</v>
-      </c>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AF6" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="12"/>
+    </row>
+    <row r="7" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="N7" s="22"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="1">
-        <v>5</v>
-      </c>
-      <c r="U7" s="1">
-        <v>8</v>
-      </c>
-      <c r="V7" s="1">
-        <v>6</v>
-      </c>
-      <c r="W7" s="1">
-        <v>7</v>
-      </c>
-      <c r="X7" s="1">
-        <v>8</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>7</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AE7" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AF7" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>8</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="AC7" s="14"/>
+    </row>
+    <row r="8" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="1">
-        <v>6</v>
-      </c>
-      <c r="U8" s="1">
-        <v>8</v>
-      </c>
-      <c r="V8" s="1">
-        <v>6</v>
-      </c>
-      <c r="W8" s="1">
-        <v>9</v>
-      </c>
-      <c r="X8" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>9</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AE8" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF8" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="1">
-        <v>7</v>
-      </c>
-      <c r="U9" s="1">
-        <v>7</v>
-      </c>
-      <c r="V9" s="1">
-        <v>6</v>
-      </c>
-      <c r="W9" s="1">
-        <v>7</v>
-      </c>
-      <c r="X9" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>7</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>8</v>
-      </c>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="12">
-        <v>-1</v>
-      </c>
-      <c r="AC9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="12"/>
-      <c r="AE9" s="12">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF9" s="12">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="AC8" s="14"/>
+    </row>
+    <row r="9" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="11"/>
+      <c r="AH9" s="11"/>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>0</v>
-      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="1">
-        <v>8</v>
-      </c>
-      <c r="U10" s="1">
-        <v>9</v>
-      </c>
-      <c r="V10" s="1">
-        <v>6</v>
-      </c>
-      <c r="W10" s="1">
-        <v>9</v>
-      </c>
-      <c r="X10" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>9</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>8</v>
-      </c>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AF10" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>5</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="AC10" s="14"/>
+    </row>
+    <row r="11" spans="2:34" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>17</v>
-      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="1">
-        <v>9</v>
-      </c>
-      <c r="AA11" s="14"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <v>4</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="1">
-        <v>10</v>
-      </c>
-      <c r="AA12" s="14"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <v>3</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="1">
-        <v>11</v>
-      </c>
-      <c r="AA13" s="14"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <v>2</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="1">
-        <v>12</v>
-      </c>
-      <c r="AA14" s="14"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="1">
-        <v>13</v>
-      </c>
-      <c r="AA15" s="14"/>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>0</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-    </row>
-    <row r="17" spans="2:16" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="9">
-        <v>0</v>
-      </c>
-      <c r="C17" s="9">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9">
-        <v>2</v>
-      </c>
-      <c r="E17" s="9">
-        <v>3</v>
-      </c>
-      <c r="F17" s="9">
-        <v>4</v>
-      </c>
-      <c r="G17" s="9">
-        <v>5</v>
-      </c>
-      <c r="H17" s="9">
-        <v>6</v>
-      </c>
-      <c r="I17" s="9">
-        <v>7</v>
-      </c>
-      <c r="J17" s="9">
-        <v>8</v>
-      </c>
-      <c r="K17" s="9">
-        <v>9</v>
-      </c>
-      <c r="L17" s="9">
-        <v>10</v>
-      </c>
-      <c r="M17" s="9">
-        <v>11</v>
-      </c>
-      <c r="N17" s="9">
-        <v>12</v>
-      </c>
-      <c r="O17" s="9">
-        <v>13</v>
-      </c>
-      <c r="P17" s="9">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+    </row>
+    <row r="12" spans="2:34" s="9" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="R1:R15"/>
-    <mergeCell ref="S1:S15"/>
-    <mergeCell ref="AA1:AA15"/>
-    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="T1:T10"/>
+    <mergeCell ref="U1:U10"/>
+    <mergeCell ref="AC1:AC10"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA70B1A-3344-4CF1-B2D8-E8CC7A854B14}">
+  <dimension ref="A2:N30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="12" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="3.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>27</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
+        <v>24</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>18</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>17</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>15</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30">
+        <v>7</v>
+      </c>
+      <c r="K30">
+        <v>8</v>
+      </c>
+      <c r="L30">
+        <v>9</v>
+      </c>
+      <c r="M30">
+        <v>10</v>
+      </c>
+      <c r="N30">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A510AC44-9A2C-498D-AF64-801DD9544E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDC4998-BF39-4D64-8864-EC1506421D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="570" yWindow="4290" windowWidth="20910" windowHeight="11835" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="26">
   <si>
     <t>x</t>
   </si>
@@ -156,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -172,6 +172,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -242,18 +248,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -270,7 +264,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -626,31 +635,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="15" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14"/>
+      <c r="I1" s="20"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="14"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="20"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -686,13 +695,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="20">
         <v>6</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="20">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -727,9 +736,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -765,9 +774,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -803,9 +812,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -841,9 +850,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -873,13 +882,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="20">
         <v>3</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="20">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -913,9 +922,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -951,9 +960,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -989,9 +998,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1027,9 +1036,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1065,9 +1074,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1097,13 +1106,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="20">
         <v>11</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="20">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1137,9 +1146,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1175,9 +1184,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1213,9 +1222,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1245,13 +1254,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="20">
         <v>12</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="20">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1286,9 +1295,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1324,9 +1333,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1362,9 +1371,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1400,9 +1409,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1430,6 +1439,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1443,11 +1457,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1501,15 +1510,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1527,9 +1536,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="AA2" s="14"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="AA2" s="20"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1550,9 +1559,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="AA3" s="14"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="AA3" s="20"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1578,9 +1587,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="AA4" s="14"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="AA4" s="20"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1606,9 +1615,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="AA5" s="14"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="AA5" s="20"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1634,9 +1643,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="AA6" s="14"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="AA6" s="20"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1662,9 +1671,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="AA7" s="14"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="AA7" s="20"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1685,9 +1694,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="AA8" s="14"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="AA8" s="20"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1708,9 +1717,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="AA9" s="14"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="AA9" s="20"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1736,9 +1745,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="AA10" s="14"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="AA10" s="20"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1759,9 +1768,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="AA11" s="14"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="AA11" s="20"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1782,9 +1791,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="AA12" s="14"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="AA12" s="20"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1805,9 +1814,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="AA13" s="14"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="AA13" s="20"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1828,9 +1837,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="AA14" s="14"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="AA14" s="20"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1851,9 +1860,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="AA15" s="14"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="AA15" s="20"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1960,31 +1969,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="15" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14"/>
+      <c r="I1" s="20"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="14"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="20"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2020,13 +2029,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="20">
         <v>5</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="20">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2061,9 +2070,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2099,9 +2108,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2137,9 +2146,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2175,9 +2184,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2207,13 +2216,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="20">
         <v>3</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="20">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2247,9 +2256,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2285,9 +2294,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2323,9 +2332,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2361,9 +2370,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2399,9 +2408,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2431,13 +2440,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="20">
         <v>11</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="20">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2471,9 +2480,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2509,9 +2518,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2547,9 +2556,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2579,13 +2588,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="20">
         <v>11</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="20">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2620,9 +2629,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2658,9 +2667,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2696,9 +2705,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2734,9 +2743,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2772,9 +2781,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2810,9 +2819,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2840,24 +2849,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2894,8 +2903,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
@@ -2911,19 +2920,19 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -2939,13 +2948,13 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="AC2" s="14"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="AC2" s="20"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="10"/>
@@ -2961,9 +2970,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="AC3" s="14"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="AC3" s="20"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -2971,8 +2980,8 @@
       <c r="AH3" s="12"/>
     </row>
     <row r="4" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="10"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -2988,9 +2997,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="AC4" s="14"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="AC4" s="20"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -2998,8 +3007,8 @@
       <c r="AH4" s="12"/>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -3015,9 +3024,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="AC5" s="14"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="AC5" s="20"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3025,8 +3034,8 @@
       <c r="AH5" s="11"/>
     </row>
     <row r="6" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="7"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -3037,14 +3046,14 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="17"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="AC6" s="14"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="AC6" s="20"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3052,38 +3061,38 @@
       <c r="AH6" s="12"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="7"/>
       <c r="E7" s="10"/>
       <c r="F7" s="7"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="22"/>
+      <c r="N7" s="18"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="AC7" s="14"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="AC7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="18"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="14"/>
       <c r="E8" s="10"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -3091,31 +3100,31 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="AC8" s="14"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="AC8" s="20"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="7"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="19"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="AC9" s="14"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="AC9" s="20"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3123,8 +3132,8 @@
       <c r="AH9" s="11"/>
     </row>
     <row r="10" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -3140,13 +3149,13 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="AC10" s="14"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="AC10" s="20"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -3180,49 +3189,51 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA70B1A-3344-4CF1-B2D8-E8CC7A854B14}">
-  <dimension ref="A2:N30"/>
+  <dimension ref="A2:N31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="12" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.42578125" customWidth="1"/>
+    <col min="14" max="14" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B2">
         <v>27</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="17" t="s">
         <v>25</v>
       </c>
       <c r="B3">
         <v>26</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3231,92 +3242,98 @@
       <c r="B4">
         <v>25</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B5">
         <v>24</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23" t="s">
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
+      <c r="J5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="B6">
         <v>23</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B7">
         <v>22</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -3325,28 +3342,22 @@
       <c r="B8">
         <v>21</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="24" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -3355,24 +3366,20 @@
       <c r="B9">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="21" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -3381,343 +3388,440 @@
       <c r="B10">
         <v>19</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>18</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="B12">
         <v>17</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="B13">
         <v>16</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="B14">
         <v>15</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>21</v>
+      </c>
       <c r="B16">
         <v>13</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="19"/>
+      <c r="D16" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="19"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="B17">
         <v>12</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C17" s="19"/>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="19"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="19"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="B18">
         <v>11</v>
       </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="B19">
         <v>10</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>9</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>8</v>
       </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>7</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>6</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="B24">
         <v>5</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="B26">
         <v>3</v>
       </c>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="B27">
         <v>2</v>
       </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>21</v>
+      </c>
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="7"/>
       <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="B29">
         <v>0</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C30">
         <v>0</v>
       </c>
@@ -3753,6 +3857,11 @@
       </c>
       <c r="N30">
         <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDC4998-BF39-4D64-8864-EC1506421D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACE178A-42C5-47A5-90A4-365A0D9438E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="4290" windowWidth="20910" windowHeight="11835" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="13845" yWindow="0" windowWidth="13845" windowHeight="16200" firstSheet="2" activeTab="5" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Tabelle2 (2)" sheetId="3" r:id="rId3"/>
     <sheet name="sectors" sheetId="1" r:id="rId4"/>
     <sheet name="Tabelle1" sheetId="5" r:id="rId5"/>
+    <sheet name="Tabelle2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="26">
   <si>
     <t>x</t>
   </si>
@@ -209,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -264,24 +265,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -635,31 +635,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="20"/>
+      <c r="I1" s="23"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="20"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="23"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -695,13 +695,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="23">
         <v>6</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="23">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -736,9 +736,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -774,9 +774,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -812,9 +812,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -850,9 +850,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -882,13 +882,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="23">
         <v>3</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="23">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -922,9 +922,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -960,9 +960,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -998,9 +998,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1036,9 +1036,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1074,9 +1074,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1106,13 +1106,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="23">
         <v>11</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="23">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1146,9 +1146,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1184,9 +1184,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1222,9 +1222,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1254,13 +1254,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="23">
         <v>12</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="23">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1295,9 +1295,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1333,9 +1333,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1371,9 +1371,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1409,9 +1409,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1439,11 +1439,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1457,6 +1452,11 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1510,15 +1510,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1536,9 +1536,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="AA2" s="20"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="AA2" s="23"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1559,9 +1559,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="AA3" s="20"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="AA3" s="23"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1587,9 +1587,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="AA4" s="20"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="AA4" s="23"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1615,9 +1615,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="AA5" s="20"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="AA5" s="23"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1643,9 +1643,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="AA6" s="20"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="AA6" s="23"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1671,9 +1671,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="AA7" s="20"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="AA7" s="23"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1694,9 +1694,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="AA8" s="20"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="AA8" s="23"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1717,9 +1717,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="AA9" s="20"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="AA9" s="23"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1745,9 +1745,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="AA10" s="20"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="AA10" s="23"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1768,9 +1768,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="AA11" s="20"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="AA11" s="23"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1791,9 +1791,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="AA12" s="20"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="AA12" s="23"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1814,9 +1814,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="AA13" s="20"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="AA13" s="23"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1837,9 +1837,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="AA14" s="20"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="AA14" s="23"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1860,9 +1860,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="AA15" s="20"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="AA15" s="23"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1969,31 +1969,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="20"/>
+      <c r="I1" s="23"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="20"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="20"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="23"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2029,13 +2029,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="23">
         <v>5</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="23">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2070,9 +2070,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2108,9 +2108,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2146,9 +2146,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2184,9 +2184,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2216,13 +2216,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="23">
         <v>3</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="23">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2256,9 +2256,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2294,9 +2294,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2332,9 +2332,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2370,9 +2370,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2408,9 +2408,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2440,13 +2440,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="23">
         <v>11</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="23">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2480,9 +2480,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2518,9 +2518,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2556,9 +2556,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2588,13 +2588,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="23">
         <v>11</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="23">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2629,9 +2629,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2667,9 +2667,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2705,9 +2705,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2743,9 +2743,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2781,9 +2781,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2819,9 +2819,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2849,24 +2849,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2920,15 +2920,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2948,9 +2948,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="AC2" s="20"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="AC2" s="23"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -2970,9 +2970,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="AC3" s="20"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="AC3" s="23"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -2997,9 +2997,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="AC4" s="20"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="AC4" s="23"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3024,9 +3024,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="AC5" s="20"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="AC5" s="23"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3051,9 +3051,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="AC6" s="20"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="AC6" s="23"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3078,9 +3078,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="AC7" s="20"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="AC7" s="23"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3100,9 +3100,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="AC8" s="20"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="AC8" s="23"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3122,9 +3122,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="AC9" s="20"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="AC9" s="23"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3149,9 +3149,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="AC10" s="20"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="AC10" s="23"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -3268,16 +3268,10 @@
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
-      <c r="I5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
@@ -3289,24 +3283,16 @@
         <v>23</v>
       </c>
       <c r="C6" s="19"/>
-      <c r="D6" s="19" t="s">
-        <v>17</v>
-      </c>
+      <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
-      <c r="J6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10" t="s">
-        <v>21</v>
-      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -3317,17 +3303,11 @@
         <v>22</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="H7" s="24"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
@@ -3343,18 +3323,22 @@
         <v>21</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="10" t="s">
-        <v>23</v>
-      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
+      <c r="J8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
@@ -3367,17 +3351,23 @@
         <v>20</v>
       </c>
       <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
+      <c r="D9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="G9" s="24" t="s">
+        <v>18</v>
+      </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="10" t="s">
-        <v>23</v>
+      <c r="I9" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
+      <c r="L9" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
     </row>
@@ -3389,15 +3379,23 @@
         <v>19</v>
       </c>
       <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+      <c r="D10" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
+      <c r="L10" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
     </row>
@@ -3407,13 +3405,25 @@
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
+      <c r="E11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="I11" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
@@ -3488,20 +3498,20 @@
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
+      <c r="I15" s="25"/>
       <c r="J15" s="19"/>
       <c r="K15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
@@ -3514,23 +3524,27 @@
         <v>13</v>
       </c>
       <c r="C16" s="19"/>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="19"/>
+      <c r="I16" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="22" t="s">
-        <v>18</v>
       </c>
       <c r="N16" s="19"/>
     </row>
@@ -3542,23 +3556,23 @@
         <v>12</v>
       </c>
       <c r="C17" s="19"/>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="10" t="s">
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="N17" s="19"/>
     </row>
@@ -3572,20 +3586,20 @@
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
       <c r="E18" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
       <c r="K18" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
@@ -3717,7 +3731,7 @@
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="24" t="s">
+      <c r="I25" s="10" t="s">
         <v>17</v>
       </c>
       <c r="J25" s="7" t="s">
@@ -3785,7 +3799,7 @@
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="23"/>
+      <c r="I28" s="21"/>
       <c r="J28" s="7" t="s">
         <v>20</v>
       </c>
@@ -3867,4 +3881,278 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A2FCF1F-A3E6-45C4-BFC8-0ABFC18A5937}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3" customWidth="1"/>
+    <col min="4" max="14" width="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="P2" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="P3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="P4" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>46</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="P5" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="P6" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="P7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="P8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>42</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>78</v>
+      </c>
+      <c r="C12">
+        <v>79</v>
+      </c>
+      <c r="D12">
+        <v>80</v>
+      </c>
+      <c r="E12">
+        <v>81</v>
+      </c>
+      <c r="F12">
+        <v>82</v>
+      </c>
+      <c r="G12">
+        <v>83</v>
+      </c>
+      <c r="H12">
+        <v>84</v>
+      </c>
+      <c r="I12">
+        <v>85</v>
+      </c>
+      <c r="J12">
+        <v>86</v>
+      </c>
+      <c r="K12">
+        <v>87</v>
+      </c>
+      <c r="L12">
+        <v>88</v>
+      </c>
+      <c r="M12">
+        <v>89</v>
+      </c>
+      <c r="N12">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACE178A-42C5-47A5-90A4-365A0D9438E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59119F86-5DBE-4374-BA23-25AFD395F238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13845" yWindow="0" windowWidth="13845" windowHeight="16200" firstSheet="2" activeTab="5" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27930" windowHeight="16440" firstSheet="2" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59119F86-5DBE-4374-BA23-25AFD395F238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B5852D-14F5-485C-89B5-382233476B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="27930" windowHeight="16440" firstSheet="2" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
@@ -129,6 +129,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -271,17 +274,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -635,31 +636,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="22" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="22" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="23"/>
+      <c r="I1" s="24"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="23"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="24"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -695,13 +696,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="24">
         <v>6</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="24">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -736,9 +737,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -774,9 +775,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -812,9 +813,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -850,9 +851,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -882,13 +883,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -922,9 +923,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -960,9 +961,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -998,9 +999,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1036,9 +1037,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1074,9 +1075,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1106,13 +1107,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="24">
         <v>11</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1146,9 +1147,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1184,9 +1185,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1222,9 +1223,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1254,13 +1255,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="24">
         <v>12</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1295,9 +1296,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1333,9 +1334,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1371,9 +1372,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1409,9 +1410,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1439,6 +1440,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1452,11 +1458,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1510,15 +1511,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1536,9 +1537,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="AA2" s="23"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="AA2" s="24"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1559,9 +1560,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="AA3" s="23"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="AA3" s="24"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1587,9 +1588,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="AA4" s="23"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="AA4" s="24"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1615,9 +1616,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="AA5" s="23"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="AA5" s="24"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1643,9 +1644,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="AA6" s="23"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="AA6" s="24"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1671,9 +1672,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="AA7" s="23"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="AA7" s="24"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1694,9 +1695,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="AA8" s="23"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="AA8" s="24"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1717,9 +1718,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="AA9" s="23"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="AA9" s="24"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1745,9 +1746,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="AA10" s="23"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="AA10" s="24"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1768,9 +1769,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="AA11" s="23"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="AA11" s="24"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1791,9 +1792,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="AA12" s="23"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="AA12" s="24"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1814,9 +1815,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="AA13" s="23"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="AA13" s="24"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1837,9 +1838,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="AA14" s="23"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="AA14" s="24"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1860,9 +1861,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="AA15" s="23"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="AA15" s="24"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1969,31 +1970,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="22" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="22" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="23"/>
+      <c r="I1" s="24"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="23"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="24"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2029,13 +2030,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="24">
         <v>5</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="24">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2070,9 +2071,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2108,9 +2109,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2146,9 +2147,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2184,9 +2185,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2216,13 +2217,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2256,9 +2257,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2294,9 +2295,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2332,9 +2333,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2370,9 +2371,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2408,9 +2409,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2440,13 +2441,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="24">
         <v>11</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2480,9 +2481,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2518,9 +2519,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2556,9 +2557,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2588,13 +2589,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="24">
         <v>11</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2629,9 +2630,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2667,9 +2668,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2705,9 +2706,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2743,9 +2744,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2781,9 +2782,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2819,9 +2820,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2849,24 +2850,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2920,15 +2921,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="24"/>
+      <c r="AC1" s="24"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2948,9 +2949,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="AC2" s="23"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="AC2" s="24"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -2970,9 +2971,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="AC3" s="23"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="AC3" s="24"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -2997,9 +2998,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="AC4" s="23"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="AC4" s="24"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3024,9 +3025,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="AC5" s="23"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="AC5" s="24"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3051,9 +3052,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="AC6" s="23"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="AC6" s="24"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3078,9 +3079,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="AC7" s="23"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="AC7" s="24"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3100,9 +3101,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="AC8" s="23"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="AC8" s="24"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3122,9 +3123,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="AC9" s="23"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="AC9" s="24"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3149,9 +3150,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="AC10" s="23"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="AC10" s="24"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -3194,7 +3195,7 @@
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="12" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.42578125" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3213,7 +3214,9 @@
       <c r="K2" s="19"/>
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
+      <c r="N2" s="19">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
@@ -3232,8 +3235,12 @@
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
+      <c r="M3" s="26">
+        <v>2.6</v>
+      </c>
+      <c r="N3" s="19">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3252,8 +3259,12 @@
       <c r="J4" s="19"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="M4" s="19">
+        <v>5</v>
+      </c>
+      <c r="N4" s="19">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
@@ -3307,7 +3318,7 @@
       <c r="E7" s="10"/>
       <c r="F7" s="7"/>
       <c r="G7" s="19"/>
-      <c r="H7" s="24"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
@@ -3356,11 +3367,11 @@
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="19"/>
@@ -3411,11 +3422,11 @@
       <c r="F11" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="22" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="25" t="s">
+      <c r="I11" s="22" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="14" t="s">
@@ -3505,7 +3516,7 @@
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="25"/>
+      <c r="I15" s="22"/>
       <c r="J15" s="19"/>
       <c r="K15" s="10" t="s">
         <v>19</v>
@@ -3528,14 +3539,14 @@
         <v>24</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="22" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="19"/>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="22" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="20" t="s">
@@ -3565,7 +3576,7 @@
         <v>19</v>
       </c>
       <c r="H17" s="19"/>
-      <c r="I17" s="25"/>
+      <c r="I17" s="22"/>
       <c r="J17" s="7" t="s">
         <v>20</v>
       </c>
@@ -3970,7 +3981,7 @@
       <c r="A5">
         <v>46</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C5">

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B5852D-14F5-485C-89B5-382233476B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AF1027-42DF-4946-A38E-487896189D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27930" windowHeight="16440" firstSheet="2" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="7080" yWindow="4620" windowWidth="11355" windowHeight="14070" firstSheet="2" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="26">
   <si>
     <t>x</t>
   </si>
@@ -160,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,12 +176,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,18 +265,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -636,31 +630,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="25" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="24"/>
+      <c r="I1" s="25"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="24"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="24"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -696,13 +690,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="25">
         <v>6</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="25">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -737,9 +731,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -775,9 +769,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -813,9 +807,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -851,9 +845,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -883,13 +877,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>3</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -923,9 +917,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -961,9 +955,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -999,9 +993,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1037,9 +1031,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1075,9 +1069,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1107,13 +1101,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="25">
         <v>11</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1147,9 +1141,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1185,9 +1179,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1223,9 +1217,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1255,13 +1249,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="25">
         <v>12</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1296,9 +1290,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1334,9 +1328,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1372,9 +1366,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1410,9 +1404,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1440,11 +1434,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1458,6 +1447,11 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1511,15 +1505,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1537,9 +1531,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="AA2" s="24"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="AA2" s="25"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1560,9 +1554,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="AA3" s="24"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="AA3" s="25"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1588,9 +1582,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="AA4" s="24"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="AA4" s="25"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1616,9 +1610,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="AA5" s="24"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="AA5" s="25"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1644,9 +1638,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="AA6" s="24"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="AA6" s="25"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1672,9 +1666,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="AA7" s="24"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="AA7" s="25"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1695,9 +1689,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="AA8" s="24"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="AA8" s="25"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1718,9 +1712,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="AA9" s="24"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="AA9" s="25"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1746,9 +1740,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="AA10" s="24"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="AA10" s="25"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1769,9 +1763,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="AA11" s="24"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="AA11" s="25"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1792,9 +1786,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="AA12" s="24"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="AA12" s="25"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1815,9 +1809,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="AA13" s="24"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="AA13" s="25"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1838,9 +1832,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="AA14" s="24"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="AA14" s="25"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1861,9 +1855,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="AA15" s="24"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="AA15" s="25"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1970,31 +1964,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="25" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="24"/>
+      <c r="I1" s="25"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="24"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="24"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2030,13 +2024,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="25">
         <v>5</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="25">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2071,9 +2065,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2109,9 +2103,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2147,9 +2141,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2185,9 +2179,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2217,13 +2211,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>3</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2257,9 +2251,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2295,9 +2289,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2333,9 +2327,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2371,9 +2365,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2409,9 +2403,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2441,13 +2435,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="25">
         <v>11</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2481,9 +2475,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2519,9 +2513,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2557,9 +2551,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2589,13 +2583,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="25">
         <v>11</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2630,9 +2624,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2668,9 +2662,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2706,9 +2700,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2744,9 +2738,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2782,9 +2776,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2820,9 +2814,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2850,24 +2844,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2921,15 +2915,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2949,9 +2943,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="AC2" s="24"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="AC2" s="25"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -2971,9 +2965,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="AC3" s="24"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="AC3" s="25"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -2998,9 +2992,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="AC4" s="24"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="AC4" s="25"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3025,9 +3019,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="AC5" s="24"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="AC5" s="25"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3052,9 +3046,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="AC6" s="24"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="AC6" s="25"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3079,9 +3073,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="AC7" s="24"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="AC7" s="25"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3101,9 +3095,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="AC8" s="24"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="AC8" s="25"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3123,9 +3117,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="AC9" s="24"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="AC9" s="25"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3150,9 +3144,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="AC10" s="24"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="AC10" s="25"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -3190,21 +3184,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA70B1A-3344-4CF1-B2D8-E8CC7A854B14}">
-  <dimension ref="A2:N31"/>
+  <dimension ref="A2:P31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="12" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="2.28515625" customWidth="1"/>
+    <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D2">
         <v>27</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
       <c r="E2" s="19"/>
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
@@ -3214,19 +3208,21 @@
       <c r="K2" s="19"/>
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
-      <c r="N2" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3">
         <v>26</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
       <c r="G3" s="19"/>
@@ -3235,46 +3231,50 @@
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="26">
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="23">
         <v>2.6</v>
       </c>
-      <c r="N3" s="19">
+      <c r="P3" s="19">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4">
         <v>25</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
       <c r="E4" s="19"/>
       <c r="F4" s="19"/>
       <c r="G4" s="19"/>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="19">
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="19">
         <v>5</v>
       </c>
-      <c r="N4" s="19">
+      <c r="P4" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5">
         <v>24</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
       <c r="E5" s="19"/>
       <c r="F5" s="19"/>
       <c r="G5" s="19"/>
@@ -3285,16 +3285,18 @@
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6">
         <v>23</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
@@ -3305,149 +3307,159 @@
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7">
         <v>22</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="19"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="10"/>
       <c r="H7" s="7"/>
       <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="19"/>
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8">
         <v>21</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
       <c r="I8" s="19"/>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
       <c r="N8" s="19"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9">
         <v>20</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="G9" s="7"/>
       <c r="H9" s="19"/>
       <c r="I9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="10" t="s">
+      <c r="K9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10">
         <v>19</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="19"/>
+      <c r="F10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="19"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="19"/>
+      <c r="K10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B11">
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D11">
         <v>18</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="H11" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="I11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="22" t="s">
+      <c r="J11" s="19"/>
+      <c r="K11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="M11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
       <c r="N11" s="19"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12">
         <v>17</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
@@ -3458,16 +3470,18 @@
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13">
         <v>16</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
@@ -3478,16 +3492,18 @@
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14">
         <v>15</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
@@ -3498,132 +3514,142 @@
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15">
         <v>14</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="22"/>
+      <c r="I15" s="19"/>
       <c r="J15" s="19"/>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="21"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="N15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16">
         <v>13</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="19"/>
+      <c r="F16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="22" t="s">
+      <c r="G16" s="7"/>
+      <c r="H16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="I16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="22" t="s">
+      <c r="J16" s="19"/>
+      <c r="K16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="20" t="s">
+      <c r="L16" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="19"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P16" s="19"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17">
         <v>12</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="19"/>
+      <c r="F17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="19"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="19"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N17" s="19"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="P17" s="19"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18">
         <v>11</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="N18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19">
         <v>10</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
@@ -3634,13 +3660,13 @@
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
       <c r="N19" s="19"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B20">
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D20">
         <v>9</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
@@ -3651,15 +3677,20 @@
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B21">
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21">
         <v>8</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
@@ -3668,15 +3699,22 @@
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
       <c r="N21" s="19"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B22">
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22">
         <v>7</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="E22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
@@ -3685,107 +3723,112 @@
       <c r="L22" s="19"/>
       <c r="M22" s="19"/>
       <c r="N22" s="19"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B23">
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23">
         <v>6</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
+      <c r="E23" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="I23" s="19"/>
       <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
       <c r="N23" s="19"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24">
+        <v>19</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24">
         <v>5</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="1"/>
       <c r="M24" s="19"/>
       <c r="N24" s="19"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25">
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25">
         <v>4</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="E25" s="19">
+        <v>3</v>
+      </c>
+      <c r="F25" s="19">
+        <v>2</v>
+      </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="7"/>
       <c r="M25" s="19"/>
       <c r="N25" s="19"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26">
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26">
         <v>3</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
+      <c r="E26" s="19">
+        <v>1</v>
+      </c>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
-      <c r="H26" s="7"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="19"/>
-      <c r="J26" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>21</v>
-      </c>
+      <c r="J26" s="7"/>
+      <c r="K26" s="19"/>
       <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
+      <c r="M26" s="10"/>
       <c r="N26" s="19"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27">
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27">
         <v>2</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
@@ -3796,98 +3839,93 @@
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
       <c r="N27" s="19"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28">
+        <v>1</v>
+      </c>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="7"/>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29">
+        <v>0</v>
+      </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>21</v>
-      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="19"/>
       <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
+      <c r="M29" s="10"/>
       <c r="N29" s="19"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
       <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
         <v>2</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>3</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>4</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>5</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>6</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>7</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>8</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>9</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>10</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>18</v>
-      </c>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -3981,7 +4019,7 @@
       <c r="A5">
         <v>46</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C5">

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AF1027-42DF-4946-A38E-487896189D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE6A047-3B9D-450A-B643-96CCA4CD93BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="4620" windowWidth="11355" windowHeight="14070" firstSheet="2" activeTab="4" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="7275" yWindow="2700" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="6" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="sectors" sheetId="1" r:id="rId4"/>
     <sheet name="Tabelle1" sheetId="5" r:id="rId5"/>
     <sheet name="Tabelle2" sheetId="6" r:id="rId6"/>
+    <sheet name="Tabelle2 (3)" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="29">
   <si>
     <t>x</t>
   </si>
@@ -124,6 +125,27 @@
   <si>
     <t>↓</t>
   </si>
+  <si>
+    <r>
+      <t>↑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>↗</t>
+    </r>
+  </si>
+  <si>
+    <t>→↘</t>
+  </si>
+  <si>
+    <t>↖↑</t>
+  </si>
 </sst>
 </file>
 
@@ -132,7 +154,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +180,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -266,16 +294,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,31 +660,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="25"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="25"/>
+      <c r="E1" s="23"/>
       <c r="F1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="25"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="25"/>
+      <c r="I1" s="23"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="25"/>
+      <c r="L1" s="23"/>
       <c r="M1" s="24"/>
-      <c r="N1" s="25"/>
+      <c r="N1" s="23"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -690,13 +720,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="23">
         <v>6</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -731,9 +761,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -769,9 +799,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -807,9 +837,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -845,9 +875,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -877,13 +907,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="23">
         <v>3</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -917,9 +947,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -955,9 +985,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -993,9 +1023,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1031,9 +1061,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1069,9 +1099,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1101,13 +1131,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="23">
         <v>11</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="23">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1141,9 +1171,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1179,9 +1209,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1217,9 +1247,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1249,13 +1279,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="23">
         <v>12</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1290,9 +1320,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1328,9 +1358,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1366,9 +1396,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1404,9 +1434,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1434,6 +1464,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1447,11 +1482,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1505,15 +1535,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1531,9 +1561,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="AA2" s="25"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="AA2" s="23"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1554,9 +1584,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="AA3" s="25"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="AA3" s="23"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1582,9 +1612,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="AA4" s="25"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="AA4" s="23"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1610,9 +1640,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="AA5" s="25"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="AA5" s="23"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1638,9 +1668,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="AA6" s="25"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="AA6" s="23"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1666,9 +1696,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="AA7" s="25"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="AA7" s="23"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1689,9 +1719,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="AA8" s="25"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="AA8" s="23"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1712,9 +1742,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="AA9" s="25"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="AA9" s="23"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1740,9 +1770,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="AA10" s="25"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="AA10" s="23"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1763,9 +1793,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="AA11" s="25"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="AA11" s="23"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1786,9 +1816,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="AA12" s="25"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="AA12" s="23"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1809,9 +1839,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="AA13" s="25"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="AA13" s="23"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1832,9 +1862,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="AA14" s="25"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="AA14" s="23"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1855,9 +1885,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="AA15" s="25"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="AA15" s="23"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1964,31 +1994,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="25"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="25"/>
+      <c r="E1" s="23"/>
       <c r="F1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="25"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="25"/>
+      <c r="I1" s="23"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="25"/>
+      <c r="L1" s="23"/>
       <c r="M1" s="24"/>
-      <c r="N1" s="25"/>
+      <c r="N1" s="23"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2024,13 +2054,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="23">
         <v>5</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2065,9 +2095,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2103,9 +2133,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2141,9 +2171,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2179,9 +2209,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2211,13 +2241,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="23">
         <v>3</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2251,9 +2281,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2289,9 +2319,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2327,9 +2357,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2365,9 +2395,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2403,9 +2433,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2435,13 +2465,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="23">
         <v>11</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="23">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2475,9 +2505,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2513,9 +2543,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2551,9 +2581,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2583,13 +2613,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="23">
         <v>11</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2624,9 +2654,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2662,9 +2692,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2700,9 +2730,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2738,9 +2768,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2776,9 +2806,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2814,9 +2844,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2844,24 +2874,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2915,15 +2945,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2943,9 +2973,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="AC2" s="25"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="AC2" s="23"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -2965,9 +2995,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="AC3" s="25"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="AC3" s="23"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -2992,9 +3022,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="AC4" s="25"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="AC4" s="23"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3019,9 +3049,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="AC5" s="25"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="AC5" s="23"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3046,9 +3076,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="AC6" s="25"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="AC6" s="23"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3073,9 +3103,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
-      <c r="AC7" s="25"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="AC7" s="23"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3095,9 +3125,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="AC8" s="25"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="AC8" s="23"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3117,9 +3147,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="AC9" s="25"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="AC9" s="23"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3144,9 +3174,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="AC10" s="25"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="AC10" s="23"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -3233,7 +3263,7 @@
       <c r="L3" s="19"/>
       <c r="M3" s="19"/>
       <c r="N3" s="19"/>
-      <c r="O3" s="23">
+      <c r="O3" s="22">
         <v>2.6</v>
       </c>
       <c r="P3" s="19">
@@ -3857,7 +3887,7 @@
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="7"/>
-      <c r="K28" s="26"/>
+      <c r="K28" s="10"/>
       <c r="L28" s="7"/>
       <c r="M28" s="19"/>
       <c r="N28" s="19"/>
@@ -3937,268 +3967,363 @@
   <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="3" customWidth="1"/>
-    <col min="4" max="14" width="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="14" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>50</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="A1" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>49</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="A2" s="1">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="P2" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>48</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>21</v>
+      </c>
       <c r="P3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>47</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="A4" s="1">
+        <v>7</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="P4" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>46</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
+      <c r="A5" s="1">
         <v>6</v>
       </c>
-      <c r="D5" s="1">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="P5" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>45</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
       <c r="P6" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>44</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="P7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>43</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="P8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>42</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="P9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>41</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="A10" s="1">
+        <v>1</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>40</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>78</v>
-      </c>
-      <c r="C12">
-        <v>79</v>
-      </c>
-      <c r="D12">
-        <v>80</v>
-      </c>
-      <c r="E12">
-        <v>81</v>
-      </c>
-      <c r="F12">
-        <v>82</v>
-      </c>
-      <c r="G12">
-        <v>83</v>
-      </c>
-      <c r="H12">
-        <v>84</v>
-      </c>
-      <c r="I12">
-        <v>85</v>
-      </c>
-      <c r="J12">
-        <v>86</v>
-      </c>
-      <c r="K12">
-        <v>87</v>
-      </c>
-      <c r="L12">
-        <v>88</v>
-      </c>
-      <c r="M12">
-        <v>89</v>
-      </c>
-      <c r="N12">
-        <v>90</v>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7</v>
+      </c>
+      <c r="J12" s="1">
+        <v>8</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10</v>
+      </c>
+      <c r="M12" s="1">
+        <v>11</v>
+      </c>
+      <c r="N12" s="1">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E1D1C4-E6E5-40B5-ACEE-4C84D6903C4B}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="P5" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>1</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7</v>
+      </c>
+      <c r="J12" s="1">
+        <v>8</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10</v>
+      </c>
+      <c r="M12" s="1">
+        <v>11</v>
+      </c>
+      <c r="N12" s="1">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE6A047-3B9D-450A-B643-96CCA4CD93BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62258C12-7289-4A6C-884F-9B370B5F3904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7275" yWindow="2700" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="6" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="7275" yWindow="2700" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="Tabelle1" sheetId="5" r:id="rId5"/>
     <sheet name="Tabelle2" sheetId="6" r:id="rId6"/>
     <sheet name="Tabelle2 (3)" sheetId="7" r:id="rId7"/>
+    <sheet name="Tabelle2 (4)" sheetId="8" r:id="rId8"/>
+    <sheet name="Tabelle2 (5)" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="29">
   <si>
     <t>x</t>
   </si>
@@ -295,17 +297,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,31 +662,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="26"/>
+      <c r="H1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="23"/>
+      <c r="I1" s="26"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="23"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -720,13 +722,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="26">
         <v>6</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="26">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -761,9 +763,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -799,9 +801,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -837,9 +839,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -875,9 +877,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -907,13 +909,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="26">
         <v>3</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="26">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -947,9 +949,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -985,9 +987,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1023,9 +1025,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1061,9 +1063,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1099,9 +1101,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1131,13 +1133,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="26">
         <v>11</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="26">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1171,9 +1173,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1209,9 +1211,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1247,9 +1249,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1279,13 +1281,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="26">
         <v>12</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="26">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1320,9 +1322,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1358,9 +1360,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1396,9 +1398,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1434,9 +1436,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1464,11 +1466,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1482,6 +1479,11 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1535,15 +1537,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1561,9 +1563,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="AA2" s="23"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="AA2" s="26"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1584,9 +1586,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="AA3" s="23"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="AA3" s="26"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1612,9 +1614,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="AA4" s="23"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="AA4" s="26"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1640,9 +1642,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="AA5" s="23"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="AA5" s="26"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1668,9 +1670,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="AA6" s="23"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+      <c r="AA6" s="26"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1696,9 +1698,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="AA7" s="23"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="AA7" s="26"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1719,9 +1721,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="AA8" s="23"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="AA8" s="26"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1742,9 +1744,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="AA9" s="23"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="AA9" s="26"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1770,9 +1772,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="AA10" s="23"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="AA10" s="26"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1793,9 +1795,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="AA11" s="23"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="26"/>
+      <c r="AA11" s="26"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1816,9 +1818,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="AA12" s="23"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="AA12" s="26"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1839,9 +1841,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="AA13" s="23"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="AA13" s="26"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1862,9 +1864,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="AA14" s="23"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="AA14" s="26"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1885,9 +1887,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="AA15" s="23"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="AA15" s="26"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1994,31 +1996,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="26"/>
+      <c r="H1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="23"/>
+      <c r="I1" s="26"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="23"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2054,13 +2056,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="26">
         <v>5</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="26">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2095,9 +2097,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2133,9 +2135,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2171,9 +2173,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2209,9 +2211,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2241,13 +2243,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="26">
         <v>3</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="26">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2281,9 +2283,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2319,9 +2321,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2357,9 +2359,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2395,9 +2397,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2433,9 +2435,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2465,13 +2467,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="26">
         <v>11</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="26">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2505,9 +2507,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2543,9 +2545,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2581,9 +2583,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2613,13 +2615,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="26">
         <v>11</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="26">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2654,9 +2656,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2692,9 +2694,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2730,9 +2732,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2768,9 +2770,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2806,9 +2808,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2844,9 +2846,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2874,24 +2876,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2945,15 +2947,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2973,9 +2975,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="AC2" s="23"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="AC2" s="26"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -2995,9 +2997,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="AC3" s="23"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="AC3" s="26"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -3022,9 +3024,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="AC4" s="23"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="AC4" s="26"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3049,9 +3051,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="AC5" s="23"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="26"/>
+      <c r="AC5" s="26"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3076,9 +3078,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="AC6" s="23"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="26"/>
+      <c r="AC6" s="26"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3103,9 +3105,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="AC7" s="23"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
+      <c r="AC7" s="26"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3125,9 +3127,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="AC8" s="23"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
+      <c r="AC8" s="26"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3147,9 +3149,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="AC9" s="23"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="AC9" s="26"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3174,9 +3176,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="AC10" s="23"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="AC10" s="26"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -4080,10 +4082,10 @@
       <c r="B10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4094,10 +4096,10 @@
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="23" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -4279,8 +4281,8 @@
         <v>18</v>
       </c>
       <c r="C11" s="17"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="11" t="s">
         <v>17</v>
       </c>
@@ -4323,6 +4325,404 @@
         <v>11</v>
       </c>
       <c r="N12" s="1">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FAFF9E-53C4-45F4-B3F1-29E7377C7220}">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>9</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>7</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="P8" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="P9" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="P10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="P12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" s="17"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1">
+        <v>7</v>
+      </c>
+      <c r="J15" s="1">
+        <v>8</v>
+      </c>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1">
+        <v>11</v>
+      </c>
+      <c r="N15" s="1">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6043FC26-B261-465E-9AB6-ECEB6C1FE2CC}">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="3" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>9</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="K5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>8</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>7</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="P12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" s="17"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1">
+        <v>7</v>
+      </c>
+      <c r="J15" s="1">
+        <v>8</v>
+      </c>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1">
+        <v>11</v>
+      </c>
+      <c r="N15" s="1">
         <v>12</v>
       </c>
     </row>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62258C12-7289-4A6C-884F-9B370B5F3904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9756B393-4F8D-4AD9-A2FF-B2C30E37DAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7275" yWindow="2700" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="29">
   <si>
     <t>x</t>
   </si>
@@ -304,10 +304,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,31 +662,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="25" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="26"/>
+      <c r="I1" s="25"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="26"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="25"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -722,13 +722,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="25">
         <v>6</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="25">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -763,9 +763,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -801,9 +801,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -839,9 +839,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -877,9 +877,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -909,13 +909,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="25">
         <v>3</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -949,9 +949,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -987,9 +987,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1025,9 +1025,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1063,9 +1063,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1101,9 +1101,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1133,13 +1133,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <v>11</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1173,9 +1173,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1211,9 +1211,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1249,9 +1249,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1281,13 +1281,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="25">
         <v>12</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1322,9 +1322,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1360,9 +1360,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1398,9 +1398,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1436,9 +1436,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1466,6 +1466,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1479,11 +1484,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1537,15 +1537,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1563,9 +1563,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="AA2" s="26"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="AA2" s="25"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1586,9 +1586,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="AA3" s="26"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="AA3" s="25"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1614,9 +1614,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="AA4" s="26"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="AA4" s="25"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1642,9 +1642,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="AA5" s="26"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="AA5" s="25"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1670,9 +1670,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="AA6" s="26"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="AA6" s="25"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1698,9 +1698,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="AA7" s="26"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="AA7" s="25"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1721,9 +1721,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="AA8" s="26"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="AA8" s="25"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1744,9 +1744,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="AA9" s="26"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="AA9" s="25"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1772,9 +1772,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="AA10" s="26"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="AA10" s="25"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1795,9 +1795,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
-      <c r="AA11" s="26"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="AA11" s="25"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1818,9 +1818,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="AA12" s="26"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="AA12" s="25"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1841,9 +1841,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
-      <c r="AA13" s="26"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="AA13" s="25"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1864,9 +1864,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="AA14" s="26"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="AA14" s="25"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1887,9 +1887,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="AA15" s="26"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="AA15" s="25"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -1996,31 +1996,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="25" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="25" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="25" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="26"/>
+      <c r="I1" s="25"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="26"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="26"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="25"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2056,13 +2056,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="25">
         <v>5</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="25">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2097,9 +2097,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2135,9 +2135,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2173,9 +2173,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2211,9 +2211,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2243,13 +2243,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="25">
         <v>3</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2283,9 +2283,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2321,9 +2321,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2359,9 +2359,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2397,9 +2397,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2435,9 +2435,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2467,13 +2467,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <v>11</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2507,9 +2507,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2545,9 +2545,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2583,9 +2583,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2615,13 +2615,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="25">
         <v>11</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2656,9 +2656,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2694,9 +2694,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2732,9 +2732,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2770,9 +2770,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2808,9 +2808,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2846,9 +2846,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="26"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2876,24 +2876,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2947,15 +2947,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2975,9 +2975,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="AC2" s="26"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="AC2" s="25"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -2997,9 +2997,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="AC3" s="26"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="AC3" s="25"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -3024,9 +3024,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="AC4" s="26"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="AC4" s="25"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3051,9 +3051,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="AC5" s="26"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="AC5" s="25"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3078,9 +3078,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="AC6" s="26"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="AC6" s="25"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3105,9 +3105,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="AC7" s="26"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="AC7" s="25"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3127,9 +3127,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="AC8" s="26"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="AC8" s="25"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3149,9 +3149,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="AC9" s="26"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="AC9" s="25"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3176,9 +3176,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="AC10" s="26"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="AC10" s="25"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -4527,7 +4527,8 @@
     <col min="6" max="6" width="2.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="14" width="3" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="1"/>
+    <col min="15" max="15" width="3.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4558,6 +4559,9 @@
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="N4" s="17" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -4567,6 +4571,9 @@
       <c r="K5" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="N5" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="P5" s="17" t="s">
         <v>25</v>
       </c>
@@ -4581,6 +4588,9 @@
       <c r="K6" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="N6" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="P6" s="1" t="s">
         <v>24</v>
       </c>
@@ -4607,6 +4617,9 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -4725,6 +4738,9 @@
       <c r="N15" s="1">
         <v>12</v>
       </c>
+      <c r="O15" s="1">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9756B393-4F8D-4AD9-A2FF-B2C30E37DAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B28CBAB-7FF9-4C20-A245-35EB0F2349D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7275" yWindow="2700" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="7095" yWindow="6225" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="29">
   <si>
     <t>x</t>
   </si>
@@ -190,7 +190,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +206,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,6 +320,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4540,23 +4558,17 @@
       <c r="A2" s="1">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="17" t="s">
@@ -4567,7 +4579,9 @@
       <c r="A5" s="1">
         <v>9</v>
       </c>
-      <c r="B5" s="11"/>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="K5" s="11" t="s">
         <v>17</v>
       </c>
@@ -4582,6 +4596,16 @@
       <c r="A6" s="1">
         <v>8</v>
       </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="J6" s="1" t="s">
         <v>20</v>
       </c>
@@ -4605,6 +4629,9 @@
       <c r="C7" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="K7" s="1" t="s">
         <v>18</v>
       </c>
@@ -4628,6 +4655,9 @@
       <c r="E8" s="11" t="s">
         <v>17</v>
       </c>
+      <c r="F8" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="P8" s="17" t="s">
         <v>19</v>
       </c>
@@ -4645,6 +4675,9 @@
       <c r="D9" s="17" t="s">
         <v>19</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="P9" s="17" t="s">
         <v>21</v>
       </c>
@@ -4656,8 +4689,8 @@
       <c r="B10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>19</v>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>22</v>
@@ -4670,6 +4703,9 @@
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C11" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="P11" s="1" t="s">
         <v>20</v>
       </c>
@@ -4678,6 +4714,9 @@
       <c r="A12" s="1">
         <v>2</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="17"/>
       <c r="P12" s="1" t="s">
         <v>18</v>
@@ -4687,11 +4726,16 @@
       <c r="A13" s="1">
         <v>1</v>
       </c>
-      <c r="B13" s="17"/>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>0</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="23"/>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B28CBAB-7FF9-4C20-A245-35EB0F2349D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BBC239-718A-4B9E-BA05-7252B529629E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7095" yWindow="6225" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="7095" yWindow="4755" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -315,16 +315,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -680,31 +680,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="25"/>
+      <c r="I1" s="28"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="25"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="28"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -740,13 +740,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="28">
         <v>6</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="28">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -781,9 +781,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -819,9 +819,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -857,9 +857,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -895,9 +895,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -927,13 +927,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="28">
         <v>3</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="28">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -967,9 +967,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1005,9 +1005,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1043,9 +1043,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1081,9 +1081,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1119,9 +1119,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1151,13 +1151,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="28">
         <v>11</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="28">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1191,9 +1191,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1229,9 +1229,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1267,9 +1267,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1299,13 +1299,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="28">
         <v>12</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="28">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1340,9 +1340,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1378,9 +1378,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1416,9 +1416,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1454,9 +1454,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1484,11 +1484,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1502,6 +1497,11 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1555,15 +1555,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1581,9 +1581,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="AA2" s="25"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="AA2" s="28"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1604,9 +1604,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="AA3" s="25"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="AA3" s="28"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1632,9 +1632,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="AA4" s="25"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="AA4" s="28"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1660,9 +1660,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="AA5" s="25"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="AA5" s="28"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1688,9 +1688,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="AA6" s="25"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="AA6" s="28"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1716,9 +1716,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="AA7" s="25"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="AA7" s="28"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1739,9 +1739,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="AA8" s="25"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="AA8" s="28"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1762,9 +1762,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="AA9" s="25"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="AA9" s="28"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1790,9 +1790,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="AA10" s="25"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="AA10" s="28"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1813,9 +1813,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="AA11" s="25"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="AA11" s="28"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1836,9 +1836,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="AA12" s="25"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="AA12" s="28"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1859,9 +1859,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="AA13" s="25"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="AA13" s="28"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1882,9 +1882,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="AA14" s="25"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="AA14" s="28"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1905,9 +1905,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="AA15" s="25"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="AA15" s="28"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -2014,31 +2014,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="25"/>
+      <c r="I1" s="28"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="25"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="28"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2074,13 +2074,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="28">
         <v>5</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="28">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2115,9 +2115,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2153,9 +2153,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2191,9 +2191,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2229,9 +2229,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2261,13 +2261,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="28">
         <v>3</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="28">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2301,9 +2301,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2339,9 +2339,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2377,9 +2377,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2415,9 +2415,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2453,9 +2453,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2485,13 +2485,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="28">
         <v>11</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="28">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2525,9 +2525,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2563,9 +2563,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2601,9 +2601,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2633,13 +2633,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="28">
         <v>11</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="28">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2674,9 +2674,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2712,9 +2712,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2750,9 +2750,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2788,9 +2788,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2826,9 +2826,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2864,9 +2864,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2894,24 +2894,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B19"/>
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="B21:B27"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2965,15 +2965,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2993,9 +2993,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="AC2" s="25"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="AC2" s="28"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -3015,9 +3015,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="AC3" s="25"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="AC3" s="28"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -3042,9 +3042,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="AC4" s="25"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="AC4" s="28"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3069,9 +3069,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="AC5" s="25"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="AC5" s="28"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3096,9 +3096,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="AC6" s="25"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="AC6" s="28"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3123,9 +3123,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
-      <c r="AC7" s="25"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="AC7" s="28"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3145,9 +3145,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="AC8" s="25"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="AC8" s="28"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3167,9 +3167,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="AC9" s="25"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="AC9" s="28"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3194,9 +3194,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="AC10" s="25"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="AC10" s="28"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -4596,7 +4596,7 @@
       <c r="A6" s="1">
         <v>8</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="17" t="s">
         <v>21</v>
       </c>
@@ -4734,7 +4734,7 @@
       <c r="A14" s="1">
         <v>0</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="26" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="17"/>

--- a/sectoren vorlage.xlsx
+++ b/sectoren vorlage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Git_Repositories\Fachinformatiker_2023_Yalikun_Abula\2023-yalikun-abula\springBoot\ocean-explorer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Documents\Java\SpringBoot3\ocean-explorer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BBC239-718A-4B9E-BA05-7252B529629E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0985A0B-518D-4392-A70E-DEF03EAA1816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7095" yWindow="4755" windowWidth="21600" windowHeight="12645" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
+    <workbookView xWindow="14475" yWindow="2130" windowWidth="11355" windowHeight="14070" firstSheet="2" activeTab="8" xr2:uid="{CE7404B4-C4A0-4B6E-9CA3-B25732518FF2}"/>
   </bookViews>
   <sheets>
     <sheet name="do not delete" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="29">
   <si>
     <t>x</t>
   </si>
@@ -322,10 +322,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,31 +680,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="27" t="s">
+      <c r="G1" s="27"/>
+      <c r="H1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="28"/>
+      <c r="I1" s="27"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="28"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="27"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -740,13 +740,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>6</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="27">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -781,9 +781,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -819,9 +819,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:D25" si="0">K4</f>
         <v>-1</v>
@@ -857,9 +857,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -895,9 +895,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -927,13 +927,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>3</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -967,9 +967,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1005,9 +1005,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1043,9 +1043,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1081,9 +1081,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1119,9 +1119,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1151,13 +1151,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>11</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -1191,9 +1191,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1229,9 +1229,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1267,9 +1267,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1299,13 +1299,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>12</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <v>10</v>
       </c>
       <c r="D21" s="3">
@@ -1340,9 +1340,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1378,9 +1378,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1416,9 +1416,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1454,9 +1454,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -1484,6 +1484,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="C21:C25"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="B3:B7"/>
@@ -1497,11 +1502,6 @@
     <mergeCell ref="C16:C19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1555,15 +1555,15 @@
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="B2" s="7"/>
@@ -1581,9 +1581,9 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="AA2" s="28"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="AA2" s="27"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -1604,9 +1604,9 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="AA3" s="28"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="AA3" s="27"/>
       <c r="AB3" s="12"/>
       <c r="AC3" s="12"/>
       <c r="AD3" s="12"/>
@@ -1632,9 +1632,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="AA4" s="28"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="AA4" s="27"/>
       <c r="AB4" s="12"/>
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
@@ -1660,9 +1660,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="AA5" s="28"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="AA5" s="27"/>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
@@ -1688,9 +1688,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="AA6" s="28"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="AA6" s="27"/>
       <c r="AB6" s="12"/>
       <c r="AC6" s="12"/>
       <c r="AD6" s="12"/>
@@ -1716,9 +1716,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="AA7" s="28"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="AA7" s="27"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -1739,9 +1739,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="AA8" s="28"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="AA8" s="27"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
@@ -1762,9 +1762,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="AA9" s="28"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="AA9" s="27"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
@@ -1790,9 +1790,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="AA10" s="28"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="AA10" s="27"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -1813,9 +1813,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="AA11" s="28"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="AA11" s="27"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -1836,9 +1836,9 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="AA12" s="28"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="AA12" s="27"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -1859,9 +1859,9 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="AA13" s="28"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="AA13" s="27"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -1882,9 +1882,9 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="AA14" s="28"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="AA14" s="27"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
@@ -1905,9 +1905,9 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="AA15" s="28"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="AA15" s="27"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
@@ -2014,31 +2014,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="27" t="s">
+      <c r="C1" s="27"/>
+      <c r="D1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="27"/>
+      <c r="F1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="27" t="s">
+      <c r="G1" s="27"/>
+      <c r="H1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="28"/>
+      <c r="I1" s="27"/>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="28"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="27"/>
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2074,13 +2074,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="27">
         <v>5</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="27">
         <v>9</v>
       </c>
       <c r="D3" s="3">
@@ -2115,9 +2115,9 @@
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
       <c r="D4" s="3">
         <f>K3</f>
         <v>-1</v>
@@ -2153,9 +2153,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="3">
         <f t="shared" ref="D5:E25" si="0">K4</f>
         <v>-1</v>
@@ -2191,9 +2191,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2229,9 +2229,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2261,13 +2261,13 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>3</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>6</v>
       </c>
       <c r="D9" s="3">
@@ -2301,9 +2301,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2339,9 +2339,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2377,9 +2377,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2415,9 +2415,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2453,9 +2453,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2485,13 +2485,13 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <v>11</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <v>7</v>
       </c>
       <c r="D16" s="3">
@@ -2525,9 +2525,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2563,9 +2563,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2601,9 +2601,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2633,13 +2633,13 @@
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <v>11</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <v>13</v>
       </c>
       <c r="D21" s="3">
@@ -2674,9 +2674,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2712,9 +2712,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -2750,9 +2750,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2788,9 +2788,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2826,9 +2826,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
       <c r="D26" s="3">
         <f>K25</f>
         <v>0</v>
@@ -2864,9 +2864,9 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
       <c r="D27" s="3">
         <f t="shared" ref="D27:E27" si="12">K26</f>
         <v>0</v>
@@ -2894,24 +2894,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:C14"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2965,15 +2965,15 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
     </row>
     <row r="2" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
@@ -2993,9 +2993,9 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="AC2" s="28"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B3" s="16"/>
@@ -3015,9 +3015,9 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="AC3" s="28"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="AC3" s="27"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="12"/>
       <c r="AF3" s="12"/>
@@ -3042,9 +3042,9 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="AC4" s="28"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="AC4" s="27"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12"/>
       <c r="AF4" s="12"/>
@@ -3069,9 +3069,9 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="AC5" s="28"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="AC5" s="27"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
@@ -3096,9 +3096,9 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="AC6" s="28"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="AC6" s="27"/>
       <c r="AD6" s="12"/>
       <c r="AE6" s="12"/>
       <c r="AF6" s="12"/>
@@ -3123,9 +3123,9 @@
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="AC7" s="28"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="AC7" s="27"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
@@ -3145,9 +3145,9 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28"/>
-      <c r="AC8" s="28"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="AC8" s="27"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
@@ -3167,9 +3167,9 @@
       <c r="P9" s="13"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28"/>
-      <c r="AC9" s="28"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="AC9" s="27"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -3194,9 +3194,9 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="AC10" s="28"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="AC10" s="27"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
@@ -4553,15 +4553,30 @@
       <c r="A1" s="1">
         <v>13</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>12</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
